--- a/tests/fixtures/sample_workbook.xlsx
+++ b/tests/fixtures/sample_workbook.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="DJ" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="4315 Utilizacion " sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,61 +414,115 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A11:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>CONCEPTO</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>VALOR MAXIMO AUTORIZADO</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>PRECIO 1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>no tocar</t>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>PRECIO 2</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONCEPTO DE EJEMPLO 1</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
+    <row r="12">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ORDENES/TICKET</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ORDENES/TICKET</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CONCEPTO A</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>100.5</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>50.25</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>TEXTO PLACEHOLDER A</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>TEXTO PLACEHOLDER A (precio 2)</t>
+        </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CONCEPTO DE EJEMPLO 2 (no mapeado en los tests)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CONCEPTO B (no mapeado en los tests)</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="n">
         <v>200</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>75.5</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>TEXTO PLACEHOLDER B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CONCEPTO C (combinado verticalmente)</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TEXTO PLACEHOLDER C1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="G16" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>TEXTO PLACEHOLDER C2</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AA88"/>
   <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A15:A16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
